--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,9 +789,348 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137270038</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87359</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>701880</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6359481</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270038</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137273132</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87359</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>701835</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6359484</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273132</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137273133</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>701795</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6359508</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273133</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,45 +791,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137270038</v>
+        <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87359</v>
+        <v>87535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701880</v>
+        <v>701840</v>
       </c>
       <c r="R3" t="n">
-        <v>6359481</v>
+        <v>6359549</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,62 +889,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270038</t>
+          <t>https://artportalen.se/Sighting/137291134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137273132</v>
+        <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87359</v>
+        <v>87535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701835</v>
+        <v>701852</v>
       </c>
       <c r="R4" t="n">
-        <v>6359484</v>
+        <v>6359490</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,22 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,62 +1004,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273132</t>
+          <t>https://artportalen.se/Sighting/137291136</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137273133</v>
+        <v>137291139</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>87535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4188</v>
+        <v>1988</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lojsta bjärs, Gtl</t>
+          <t>lojsta, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701795</v>
+        <v>701901</v>
       </c>
       <c r="R5" t="n">
-        <v>6359508</v>
+        <v>6359404</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,18 +1119,1501 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137291139</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137291140</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91929</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>701905</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6359382</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291140</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137287624</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>701944</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6359214</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137287624</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137291131</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>701811</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6359565</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291131</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137291137</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>701885</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6359443</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291137</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137291141</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>701914</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6359324</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291141</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137291143</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87522</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>701933</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6359454</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291143</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137270038</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87359</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701880</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6359481</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Anna Helmersson, Ulla Sebestyen, Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270038</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137273132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87359</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701835</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6359484</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273132</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137291142</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87359</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701933</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6359378</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291142</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137273133</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsta bjärs, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701795</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6359508</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137273133</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137291147</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91542</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>701959</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6359388</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291147</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137291135</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92937</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>701858</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6359511</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137291138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87475</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>701908</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6359414</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291138</t>
         </is>
       </c>
     </row>
@@ -1131,6 +2623,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,32 +1021,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137291139</v>
+        <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>87535</v>
+        <v>91939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1988</v>
+        <v>2015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701901</v>
+        <v>701905</v>
       </c>
       <c r="R5" t="n">
-        <v>6359404</v>
+        <v>6359382</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,16 +1130,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291139</t>
+          <t>https://artportalen.se/Sighting/137291140</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137291140</v>
+        <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,23 +1164,31 @@
           <t>Peck</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>lojsta, Gtl</t>
+          <t>Lojsta hed, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701905</v>
+        <v>701900</v>
       </c>
       <c r="R6" t="n">
-        <v>6359382</v>
+        <v>6359381</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,45 +1215,36 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicolai Berg</t>
+          <t>Oskar Karl Elias Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+          <t>Oskar Karl Elias Olsson, Nicolai Berg, Meandra Sewell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137291140</t>
+          <t>https://artportalen.se/Sighting/137311968</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1938,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2277,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>91552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92937</v>
+        <v>92947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,6 +2613,122 @@
       <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137291138</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137291139</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>lojsta, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>701901</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6359404</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nicolai Berg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nicolai Berg, Oskar Karl Elias Olsson, Meandra Sewell</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137291139</t>
         </is>
       </c>
     </row>
@@ -2636,6 +2751,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92947</v>
+        <v>92948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92948</v>
+        <v>92951</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92951</v>
+        <v>92953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 447-2023 artfynd.xlsx
+++ b/artfynd/A 447-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137291134</v>
       </c>
       <c r="B3" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>137291136</v>
       </c>
       <c r="B4" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137291140</v>
       </c>
       <c r="B5" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>137311968</v>
       </c>
       <c r="B6" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137287624</v>
       </c>
       <c r="B7" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137291131</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>137291137</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137291141</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>137291143</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137270038</v>
       </c>
       <c r="B12" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137273132</v>
       </c>
       <c r="B13" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137291142</v>
       </c>
       <c r="B14" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>137273133</v>
       </c>
       <c r="B15" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137291147</v>
       </c>
       <c r="B16" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>137291135</v>
       </c>
       <c r="B17" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>137291138</v>
       </c>
       <c r="B18" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137291139</v>
       </c>
       <c r="B19" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
